--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.59509164292017</v>
+        <v>7.734202391974528</v>
       </c>
       <c r="D2" t="n">
-        <v>28.429737951659</v>
+        <v>4.619832417144588</v>
       </c>
       <c r="E2" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F2" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.67004269089983</v>
+        <v>9.371381937271222</v>
       </c>
       <c r="D3" t="n">
-        <v>58.19076412839311</v>
+        <v>9.45599917086388</v>
       </c>
       <c r="E3" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F3" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.67227910279563</v>
+        <v>9.04674535420429</v>
       </c>
       <c r="D4" t="n">
-        <v>36.47259244967377</v>
+        <v>5.926796273071988</v>
       </c>
       <c r="E4" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F4" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.23981165594108</v>
+        <v>5.563969394090425</v>
       </c>
       <c r="D5" t="n">
-        <v>27.61340254296815</v>
+        <v>4.487177913232325</v>
       </c>
       <c r="E5" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F5" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.66981726869481</v>
+        <v>5.958845306162907</v>
       </c>
       <c r="D6" t="n">
-        <v>18.9274932307477</v>
+        <v>3.075717649996502</v>
       </c>
       <c r="E6" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F6" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.56346014966983</v>
+        <v>4.804062274321347</v>
       </c>
       <c r="D7" t="n">
-        <v>28.6530975637888</v>
+        <v>4.656128354115681</v>
       </c>
       <c r="E7" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F7" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.20426580082809</v>
+        <v>4.583193192634564</v>
       </c>
       <c r="D8" t="n">
-        <v>13.97338427090588</v>
+        <v>2.270674944022205</v>
       </c>
       <c r="E8" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F8" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.36815823642023</v>
+        <v>3.959825713418288</v>
       </c>
       <c r="D9" t="n">
-        <v>20.27401876704701</v>
+        <v>3.294528049645139</v>
       </c>
       <c r="E9" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F9" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55468745072683</v>
+        <v>7.24013671074311</v>
       </c>
       <c r="D10" t="n">
-        <v>45.22961514395892</v>
+        <v>7.349812460893325</v>
       </c>
       <c r="E10" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F10" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4.89995286294416</v>
+        <v>0.796242340228426</v>
       </c>
       <c r="D11" t="n">
-        <v>4.946486345275037</v>
+        <v>0.8038040311071936</v>
       </c>
       <c r="E11" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F11" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.3196524744529</v>
+        <v>6.876943527098597</v>
       </c>
       <c r="D12" t="n">
-        <v>30.05852041449226</v>
+        <v>4.884509567354993</v>
       </c>
       <c r="E12" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F12" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.13750750166524</v>
+        <v>3.434844969020601</v>
       </c>
       <c r="D13" t="n">
-        <v>19.03678698814675</v>
+        <v>3.093477885573847</v>
       </c>
       <c r="E13" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F13" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.2464686256473</v>
+        <v>4.102551151667686</v>
       </c>
       <c r="D14" t="n">
-        <v>25.58503812667097</v>
+        <v>4.157568695584033</v>
       </c>
       <c r="E14" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F14" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.14599858114279</v>
+        <v>2.623724769435704</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48145123312744</v>
+        <v>2.67823582538321</v>
       </c>
       <c r="E15" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F15" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>54.71345352246866</v>
+        <v>8.890936197401158</v>
       </c>
       <c r="D16" t="n">
-        <v>47.43416490252569</v>
+        <v>7.708051796660424</v>
       </c>
       <c r="E16" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F16" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>21.18919530889715</v>
+        <v>3.443244237695787</v>
       </c>
       <c r="D17" t="n">
-        <v>21.2167321472214</v>
+        <v>3.447718973923477</v>
       </c>
       <c r="E17" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F17" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.57354733452988</v>
+        <v>4.805701441861105</v>
       </c>
       <c r="D18" t="n">
-        <v>29.28157678691913</v>
+        <v>4.758256227874359</v>
       </c>
       <c r="E18" t="n">
-        <v>14.48728056809574</v>
+        <v>2.354183092315557</v>
       </c>
       <c r="F18" t="n">
-        <v>12.83032106334001</v>
+        <v>2.084927172792752</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
